--- a/module_1_scraping_engine/data/output/archetype_b_test_scraped_data.xlsx
+++ b/module_1_scraping_engine/data/output/archetype_b_test_scraped_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
+  <dimension ref="A1:M249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seattle, San Francisco, New York City</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8172510</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8172508</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:49.180032+00:00</t>
+          <t>2026-10-21T08:15:58.246778+00:00</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Seattle, San Francisco, New York City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8172487</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8172510</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:49.180032+00:00</t>
+          <t>2026-10-21T08:15:58.246778+00:00</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:53.557375+00:00</t>
+          <t>2026-10-21T08:16:01.921984+00:00</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:53.557375+00:00</t>
+          <t>2026-10-21T08:16:01.921984+00:00</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:55.166323+00:00</t>
+          <t>2026-10-21T08:16:04.510126+00:00</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:55.166323+00:00</t>
+          <t>2026-10-21T08:16:04.510126+00:00</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Account Executive, AI Native</t>
+          <t>3P Revenue Accounting &amp; Reporting</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>New York City, NY; San Francisco, CA | New York City, NY</t>
+          <t>San Francisco, CA | Seattle, WA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/4461450008</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5456619008</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:56.554983+00:00</t>
+          <t>2026-10-21T08:16:08.126640+00:00</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Account Executive - DNB</t>
+          <t>Account Executive, AI Native</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>New York City, NY; San Francisco, CA | New York City, NY</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5391376008</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4461450008</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:56.554983+00:00</t>
+          <t>2026-10-21T08:16:08.126640+00:00</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:57.900246+00:00</t>
+          <t>2026-10-21T08:16:10.886325+00:00</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:57.900246+00:00</t>
+          <t>2026-10-21T08:16:10.886325+00:00</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:58.824833+00:00</t>
+          <t>2026-10-21T08:16:11.977569+00:00</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-16T14:12:58.824833+00:00</t>
+          <t>2026-10-21T08:16:11.977569+00:00</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:00.824281+00:00</t>
+          <t>2026-10-21T08:16:13.432225+00:00</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:00.824281+00:00</t>
+          <t>2026-10-21T08:16:13.432225+00:00</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:02.445771+00:00</t>
+          <t>2026-10-21T08:16:14.859736+00:00</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:02.445771+00:00</t>
+          <t>2026-10-21T08:16:14.859736+00:00</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:03.561472+00:00</t>
+          <t>2026-10-21T08:16:15.727375+00:00</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:03.561472+00:00</t>
+          <t>2026-10-21T08:16:15.727375+00:00</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:04.854579+00:00</t>
+          <t>2026-10-21T08:16:16.420538+00:00</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:04.854579+00:00</t>
+          <t>2026-10-21T08:16:16.420538+00:00</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:05.716272+00:00</t>
+          <t>2026-10-21T08:16:17.008236+00:00</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:05.716272+00:00</t>
+          <t>2026-10-21T08:16:17.008236+00:00</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:06.280477+00:00</t>
+          <t>2026-10-21T08:16:17.574949+00:00</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:06.280477+00:00</t>
+          <t>2026-10-21T08:16:17.574949+00:00</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:07.005379+00:00</t>
+          <t>2026-10-21T08:16:18.902883+00:00</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:07.006384+00:00</t>
+          <t>2026-10-21T08:16:18.902883+00:00</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:07.569277+00:00</t>
+          <t>2026-10-21T08:16:19.759268+00:00</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:07.569277+00:00</t>
+          <t>2026-10-21T08:16:19.759268+00:00</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Associate Legal Counsel, Japan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8184174?gh_jid=8184174</t>
+          <t>https://careers.airbnb.com/positions/7789554?gh_jid=7789554</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:08.185210+00:00</t>
+          <t>2026-10-21T08:16:20.389231+00:00</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Associate Legal Counsel, Japan</t>
+          <t>Associate Principal, Procurement Innovation Supplier Programs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7789554?gh_jid=7789554</t>
+          <t>https://careers.airbnb.com/positions/8231416?gh_jid=8231416</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Financial Planning and Analysis</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:08.185210+00:00</t>
+          <t>2026-10-21T08:16:20.389231+00:00</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chief of Staff to GM, Ads</t>
+          <t>Administrative Business Partner I - Communications and Growth Marketing</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US; Remote, US</t>
+          <t>Los Angeles, CA US</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7488432</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8280238</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>EPD Ads and Ads Product</t>
+          <t>Communications</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:08.766500+00:00</t>
+          <t>2026-10-21T08:16:21.262975+00:00</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Client Account Manager, Enterprise Sales - Italian Market</t>
+          <t>Chief of Staff to GM, Ads</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dublin, IE</t>
+          <t>San Francisco, CA, US</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8135500</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7488432</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Europe Enterprise Sales</t>
+          <t>EPD Ads and Ads Product</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:08.766500+00:00</t>
+          <t>2026-10-21T08:16:21.262975+00:00</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:10.370976+00:00</t>
+          <t>2026-10-21T08:16:21.854651+00:00</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:10.370976+00:00</t>
+          <t>2026-10-21T08:16:21.854651+00:00</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:10.902105+00:00</t>
+          <t>2026-10-21T08:16:22.743819+00:00</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:10.902105+00:00</t>
+          <t>2026-10-21T08:16:22.743819+00:00</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:11.501510+00:00</t>
+          <t>2026-10-21T08:16:23.230868+00:00</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:11.501510+00:00</t>
+          <t>2026-10-21T08:16:23.230868+00:00</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:12.839985+00:00</t>
+          <t>2026-10-21T08:16:23.776927+00:00</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:12.839985+00:00</t>
+          <t>2026-10-21T08:16:23.777932+00:00</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:13.457322+00:00</t>
+          <t>2026-10-21T08:16:24.259255+00:00</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:13.457322+00:00</t>
+          <t>2026-10-21T08:16:24.259255+00:00</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:13.928146+00:00</t>
+          <t>2026-10-21T08:16:25.596413+00:00</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:13.928146+00:00</t>
+          <t>2026-10-21T08:16:25.596413+00:00</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Benefits Advising (Renewals) Leader</t>
+          <t>AI Operations Program Manager, Benefits</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8078212</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/7899871</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:14.443350+00:00</t>
+          <t>2026-10-21T08:16:26.069005+00:00</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Business Development Representative</t>
+          <t>Benefits Advising (Renewals) Leader</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gusto/jobs/8002008</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/8078212</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Experience</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:14.443350+00:00</t>
+          <t>2026-10-21T08:16:26.069005+00:00</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:14.917908+00:00</t>
+          <t>2026-10-21T08:16:26.692527+00:00</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:14.918911+00:00</t>
+          <t>2026-10-21T08:16:26.692527+00:00</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:15.827626+00:00</t>
+          <t>2026-10-21T08:16:27.125289+00:00</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:15.827626+00:00</t>
+          <t>2026-10-21T08:16:27.125289+00:00</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:16.218710+00:00</t>
+          <t>2026-10-21T08:16:27.587133+00:00</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Account Management Intern - Summer 2027</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/uberfreight/jobs/5434731008</t>
+          <t>https://job-boards.greenhouse.io/uberfreight/jobs/5444034008</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:16.218710+00:00</t>
+          <t>2026-10-21T08:16:27.588132+00:00</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:16.729278+00:00</t>
+          <t>2026-10-21T08:16:28.120089+00:00</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:16.729278+00:00</t>
+          <t>2026-10-21T08:16:28.120089+00:00</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:17.213313+00:00</t>
+          <t>2026-10-21T08:16:28.598405+00:00</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:17.214314+00:00</t>
+          <t>2026-10-21T08:16:28.598405+00:00</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:17.706613+00:00</t>
+          <t>2026-10-21T08:16:29.138790+00:00</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Director, Head of Creative</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3892,17 +3892,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8792309002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8900429002</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t xml:space="preserve">Community Growth </t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:17.706613+00:00</t>
+          <t>2026-10-21T08:16:29.138790+00:00</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:18.202217+00:00</t>
+          <t>2026-10-21T08:16:29.605915+00:00</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Remote - Canada: Select locations</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/8048847?gh_jid=8048847</t>
+          <t>https://jobs.dropbox.com/listing/8048848?gh_jid=8048848</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:18.202217+00:00</t>
+          <t>2026-10-21T08:16:29.605915+00:00</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:18.787417+00:00</t>
+          <t>2026-10-21T08:16:30.068389+00:00</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:18.787417+00:00</t>
+          <t>2026-10-21T08:16:30.068389+00:00</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Systems Engineer – Runtime Frameworks &amp; Resource Intelligence</t>
+          <t>Agentic AI Systems Evaluation Engineer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/hp/jobs/6218769004</t>
+          <t>https://job-boards.greenhouse.io/hp/jobs/6228405004</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:19.449198+00:00</t>
+          <t>2026-10-21T08:16:30.582931+00:00</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer, Agentic Computing Foundation</t>
+          <t>AI Runtime and ML Model Systems Engineer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/hp/jobs/6214653004</t>
+          <t>https://job-boards.greenhouse.io/hp/jobs/6226714004</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:19.449198+00:00</t>
+          <t>2026-10-21T08:16:30.582931+00:00</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:19.764264+00:00</t>
+          <t>2026-10-21T08:16:31.070819+00:00</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:19.764264+00:00</t>
+          <t>2026-10-21T08:16:31.070819+00:00</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:20.289352+00:00</t>
+          <t>2026-10-21T08:16:31.573474+00:00</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:20.289352+00:00</t>
+          <t>2026-10-21T08:16:31.573474+00:00</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:21.126904+00:00</t>
+          <t>2026-10-21T08:16:32.833830+00:00</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:21.126904+00:00</t>
+          <t>2026-10-21T08:16:32.833830+00:00</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:21.725502+00:00</t>
+          <t>2026-10-21T08:16:33.433898+00:00</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:21.726510+00:00</t>
+          <t>2026-10-21T08:16:33.433898+00:00</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:23.697353+00:00</t>
+          <t>2026-10-21T08:16:34.647344+00:00</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.samsara.com/company/careers/roles/7618026?gh_jid=7618026</t>
+          <t>https://www.samsara.com/company/careers/roles/8260850?gh_jid=8260850</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:23.698353+00:00</t>
+          <t>2026-10-21T08:16:34.647344+00:00</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:24.023125+00:00</t>
+          <t>2026-10-21T08:16:34.974267+00:00</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:24.023125+00:00</t>
+          <t>2026-10-21T08:16:34.974267+00:00</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:24.691861+00:00</t>
+          <t>2026-10-21T08:16:35.535437+00:00</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:24.691861+00:00</t>
+          <t>2026-10-21T08:16:35.535437+00:00</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:25.076409+00:00</t>
+          <t>2026-10-21T08:16:35.993105+00:00</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:25.076409+00:00</t>
+          <t>2026-10-21T08:16:35.993105+00:00</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Animation Systems Programmer</t>
+          <t>Backend Services Programmer Intern</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Larkspur,California,United States</t>
+          <t>Cary,North Carolina,United States</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6103058004?gh_jid=6103058004</t>
+          <t>https://epicgames.com/careers/jobs/6183293004?gh_jid=6183293004</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:25.941650+00:00</t>
+          <t>2026-10-21T08:16:36.625130+00:00</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Backend Services Programmer Intern</t>
+          <t>Cinematics Director</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cary,North Carolina,United States</t>
+          <t>BLANK,BLANK,Multiple Locations</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://epicgames.com/careers/jobs/6183293004?gh_jid=6183293004</t>
+          <t>https://epicgames.com/careers/jobs/5993483004?gh_jid=5993483004</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Engineering Generalist</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:25.941650+00:00</t>
+          <t>2026-10-21T08:16:36.625130+00:00</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:26.287540+00:00</t>
+          <t>2026-10-21T08:16:36.975589+00:00</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:26.820484+00:00</t>
+          <t>2026-10-21T08:16:37.492193+00:00</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Commercial Counsel, APAC</t>
+          <t>Brand Designer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Singapore (Hybrid)</t>
+          <t>London, UK (Hybrid)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mixpanel/jobs/8172398</t>
+          <t>https://job-boards.greenhouse.io/mixpanel/jobs/8207178</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:28.007739+00:00</t>
+          <t>2026-10-21T08:16:38.078453+00:00</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Customer Engineer</t>
+          <t>Commercial Counsel, APAC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Remote, US (Remote)</t>
+          <t>Singapore (Hybrid)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mixpanel/jobs/8142661</t>
+          <t>https://job-boards.greenhouse.io/mixpanel/jobs/8172398</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Customer Engineering</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:28.007739+00:00</t>
+          <t>2026-10-21T08:16:38.078453+00:00</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:28.352310+00:00</t>
+          <t>2026-10-21T08:16:38.550968+00:00</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:28.352310+00:00</t>
+          <t>2026-10-21T08:16:38.550968+00:00</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:28.904744+00:00</t>
+          <t>2026-10-21T08:16:39.214652+00:00</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:28.904744+00:00</t>
+          <t>2026-10-21T08:16:39.214652+00:00</t>
         </is>
       </c>
     </row>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>New York, New York</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://seatgeek.com/jobs/8108835?gh_jid=8108835</t>
+          <t>https://seatgeek.com/jobs/8108805?gh_jid=8108805</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:29.368895+00:00</t>
+          <t>2026-10-21T08:16:39.559347+00:00</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>New York, New York</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://seatgeek.com/jobs/8108805?gh_jid=8108805</t>
+          <t>https://seatgeek.com/jobs/8108835?gh_jid=8108835</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:29.368895+00:00</t>
+          <t>2026-10-21T08:16:39.559347+00:00</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:30.166847+00:00</t>
+          <t>2026-10-21T08:16:40.106670+00:00</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:30.166847+00:00</t>
+          <t>2026-10-21T08:16:40.106670+00:00</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:31.203904+00:00</t>
+          <t>2026-10-21T08:16:40.622511+00:00</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:31.203904+00:00</t>
+          <t>2026-10-21T08:16:40.622511+00:00</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:32.241473+00:00</t>
+          <t>2026-10-21T08:16:41.445568+00:00</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:32.241473+00:00</t>
+          <t>2026-10-21T08:16:41.445568+00:00</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:32.618218+00:00</t>
+          <t>2026-10-21T08:16:41.756045+00:00</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:32.618218+00:00</t>
+          <t>2026-10-21T08:16:41.756045+00:00</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:33.440359+00:00</t>
+          <t>2026-10-21T08:16:42.354805+00:00</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:33.440359+00:00</t>
+          <t>2026-10-21T08:16:42.354805+00:00</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:34.141796+00:00</t>
+          <t>2026-10-21T08:16:43.109850+00:00</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:34.141796+00:00</t>
+          <t>2026-10-21T08:16:43.109850+00:00</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:35.426661+00:00</t>
+          <t>2026-10-21T08:16:43.499256+00:00</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:35.426661+00:00</t>
+          <t>2026-10-21T08:16:43.499256+00:00</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:36.030345+00:00</t>
+          <t>2026-10-21T08:16:44.226572+00:00</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:36.030345+00:00</t>
+          <t>2026-10-21T08:16:44.226572+00:00</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:36.400048+00:00</t>
+          <t>2026-10-21T08:16:44.619389+00:00</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Chief of Staff, CCO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UK - Remote</t>
+          <t>USA - Remote</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/pingidentity/jobs/8783982002</t>
+          <t>https://job-boards.greenhouse.io/pingidentity/jobs/8889875002</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:36.400048+00:00</t>
+          <t>2026-10-21T08:16:44.619389+00:00</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:36.857456+00:00</t>
+          <t>2026-10-21T08:16:45.085134+00:00</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:36.857456+00:00</t>
+          <t>2026-10-21T08:16:45.085134+00:00</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:37.502237+00:00</t>
+          <t>2026-10-21T08:16:45.694012+00:00</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tanium/jobs/8233833</t>
+          <t>https://job-boards.greenhouse.io/tanium/jobs/8280249</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:37.502237+00:00</t>
+          <t>2026-10-21T08:16:45.694012+00:00</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:37.876584+00:00</t>
+          <t>2026-10-21T08:16:46.086993+00:00</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:37.876584+00:00</t>
+          <t>2026-10-21T08:16:46.086993+00:00</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:39.203330+00:00</t>
+          <t>2026-10-21T08:16:47.128830+00:00</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:39.203330+00:00</t>
+          <t>2026-10-21T08:16:47.129828+00:00</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:39.561080+00:00</t>
+          <t>2026-10-21T08:16:47.473237+00:00</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:39.561080+00:00</t>
+          <t>2026-10-21T08:16:47.473237+00:00</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Customer Success Engineer, Sydney</t>
+          <t>Analytics Business Partner</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Remote - Australia</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -7609,17 +7609,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://cribl.io/job-detail/?gh_jid=6211240004</t>
+          <t>https://cribl.io/job-detail/?gh_jid=6219915004</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Customer Experience</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:40.091444+00:00</t>
+          <t>2026-10-21T08:16:48.031392+00:00</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Customer Support Manager</t>
+          <t>Cloud Partner Sales Manager (Northeast)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Remote - United States</t>
+          <t>Remote - Philadelphia, Pennsylvania</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7668,17 +7668,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://cribl.io/job-detail/?gh_jid=6123463004</t>
+          <t>https://cribl.io/job-detail/?gh_jid=6225541004</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:40.091444+00:00</t>
+          <t>2026-10-21T08:16:48.031392+00:00</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:40.548585+00:00</t>
+          <t>2026-10-21T08:16:48.484796+00:00</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:40.548585+00:00</t>
+          <t>2026-10-21T08:16:48.484796+00:00</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:41.101881+00:00</t>
+          <t>2026-10-21T08:16:49.016130+00:00</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:41.101881+00:00</t>
+          <t>2026-10-21T08:16:49.016130+00:00</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7941,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Remote in US</t>
+          <t>Edinburgh, Scotland, United Kingdom</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://abacustechnology.com/about/careers/current-vacancies/?gh_jid=8007184003</t>
+          <t>https://abacustechnology.com/about/careers/current-vacancies/?gh_jid=8009354003</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:41.585801+00:00</t>
+          <t>2026-10-21T08:16:49.509534+00:00</t>
         </is>
       </c>
     </row>
@@ -8000,12 +8000,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Edinburgh, Scotland, United Kingdom</t>
+          <t>Remote in US</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://abacustechnology.com/about/careers/current-vacancies/?gh_jid=8009354003</t>
+          <t>https://abacustechnology.com/about/careers/current-vacancies/?gh_jid=8007184003</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:41.585801+00:00</t>
+          <t>2026-10-21T08:16:49.509534+00:00</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:42.061784+00:00</t>
+          <t>2026-10-21T08:16:49.989396+00:00</t>
         </is>
       </c>
     </row>
@@ -8150,34 +8150,34 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:42.061784+00:00</t>
+          <t>2026-10-21T08:16:49.989396+00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Webflow (Greenhouse)</t>
+          <t>Asana (Greenhouse)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GH-WEBFLOW</t>
+          <t>GH-ASANA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Account Executive, EMEA (Germany)</t>
+          <t>Administrative Business Partner</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Webflow</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>London, U.K. (Hybrid)</t>
+          <t>Vancouver, BC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8199,49 +8199,49 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/webflow/jobs/7951430</t>
+          <t>https://www.asana.com/jobs/apply/8165477?gh_jid=8165477</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>R&amp;D Executive</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:42.578069+00:00</t>
+          <t>2026-10-21T08:16:51.285206+00:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Webflow (Greenhouse)</t>
+          <t>Asana (Greenhouse)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GH-WEBFLOW</t>
+          <t>GH-ASANA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Corporate Account Executive - East</t>
+          <t>AI GTM Specialist</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Webflow</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CA Remote (BC &amp; ON only); U.S. Remote</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8258,44 +8258,44 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/webflow/jobs/6124408</t>
+          <t>https://www.asana.com/jobs/apply/8194380?gh_jid=8194380</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>AI GTM</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:42.578069+00:00</t>
+          <t>2026-10-21T08:16:51.285206+00:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Asana (Greenhouse)</t>
+          <t>ThoughtWorks (Greenhouse)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GH-ASANA</t>
+          <t>GH-THOUGHTWORKS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Administrative Business Partner</t>
+          <t>Accounts Payable (Analista de Contas a Pagar Pleno) - Contrato por prazo determinado</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>ThoughtWorks</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vancouver, BC</t>
+          <t>Brazil, Brazil</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8317,44 +8317,44 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://www.asana.com/jobs/apply/8165477?gh_jid=8165477</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8263432?gh_jid=8263432</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>R&amp;D Executive</t>
+          <t>80_TWRKS Finance</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:43.402339+00:00</t>
+          <t>2026-10-21T08:16:51.648876+00:00</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Asana (Greenhouse)</t>
+          <t>ThoughtWorks (Greenhouse)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GH-ASANA</t>
+          <t>GH-THOUGHTWORKS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AI GTM Specialist</t>
+          <t>Business Development Manager</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>ThoughtWorks</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8376,44 +8376,44 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.asana.com/jobs/apply/8194380?gh_jid=8194380</t>
+          <t>https://www.thoughtworks.com/careers/jobs/7978633?gh_jid=7978633</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>AI GTM</t>
+          <t>2K_TWSGP OPS - Public &amp; Healthcare++</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:43.402339+00:00</t>
+          <t>2026-10-21T08:16:51.648876+00:00</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ThoughtWorks (Greenhouse)</t>
+          <t>Palantir (Lever)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GH-THOUGHTWORKS</t>
+          <t>LEVER-PALANTIR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Accounts Payable (Analista de Contas a Pagar Pleno) - Contrato por prazo determinado</t>
+          <t>Administrative Business Partner</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ThoughtWorks</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Brazil, Brazil</t>
+          <t>Singapore, Singapore</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8435,44 +8435,44 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8263432?gh_jid=8263432</t>
+          <t>https://jobs.lever.co/palantir/6ed76ce8-4156-4b60-b120-403538bd66cd</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>80_TWRKS Finance</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:44.453751+00:00</t>
+          <t>2026-10-21T08:17:04.179644+00:00</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ThoughtWorks (Greenhouse)</t>
+          <t>Palantir (Lever)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GH-THOUGHTWORKS</t>
+          <t>LEVER-PALANTIR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Business Development Manager</t>
+          <t>Administrative Business Partner</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ThoughtWorks</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Amsterdam, Netherlands</t>
+          <t>London, United Kingdom</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8494,44 +8494,44 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8166611?gh_jid=8166611</t>
+          <t>https://jobs.lever.co/palantir/ac978161-6f46-4f6b-ad9e-a258e642751c</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2Y_TWNET Sales Regional Markets</t>
+          <t>Administrative</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:44.453751+00:00</t>
+          <t>2026-10-21T08:17:04.179644+00:00</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Palantir (Lever)</t>
+          <t>Paytm (Lever)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LEVER-PALANTIR</t>
+          <t>LEVER-PAYTM</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Administrative Business Partner</t>
+          <t>Account Executive/ Director - AI Agentic Enterprise Sales</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Singapore, Singapore</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>full_time employment</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -8553,44 +8553,44 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/6ed76ce8-4156-4b60-b120-403538bd66cd</t>
+          <t>https://jobs.lever.co/paytm/9eed4fec-73f7-4114-a5d3-b2f689c92e8c</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Inference and Agentic AI, Sales</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:57.172771+00:00</t>
+          <t>2026-10-21T08:17:05.506228+00:00</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Palantir (Lever)</t>
+          <t>Paytm (Lever)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LEVER-PALANTIR</t>
+          <t>LEVER-PAYTM</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Administrative Business Partner</t>
+          <t>AM/Manager– Procurement (Admin, Real Estate &amp; HR)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>London, United Kingdom</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>on_roll</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -8612,44 +8612,44 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/ac978161-6f46-4f6b-ad9e-a258e642751c</t>
+          <t>https://jobs.lever.co/paytm/feb33510-9ea7-4b69-b69d-87a41f7c2c2c</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Administrative</t>
+          <t>Non IT Purchase, Purchase</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:57.172771+00:00</t>
+          <t>2026-10-21T08:17:05.506228+00:00</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Paytm (Lever)</t>
+          <t>Spotify (Lever)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LEVER-PAYTM</t>
+          <t>LEVER-SPOTIFY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Account Executive/ Director - AI Agentic Enterprise Sales</t>
+          <t>Art Director - Mexico</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>full_time employment</t>
+          <t>permanent</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -8671,44 +8671,44 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9eed4fec-73f7-4114-a5d3-b2f689c92e8c</t>
+          <t>https://jobs.lever.co/spotify/223f9722-3579-4ff2-b123-e4cc7b0c1a64</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Inference and Agentic AI, Sales</t>
+          <t>Marketing, Markets and Subscriber Growth</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:58.323463+00:00</t>
+          <t>2026-10-21T08:17:06.523867+00:00</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Paytm (Lever)</t>
+          <t>Spotify (Lever)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LEVER-PAYTM</t>
+          <t>LEVER-SPOTIFY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AM/Manager– Procurement (Admin, Real Estate &amp; HR)</t>
+          <t>Artist &amp; Label Partnerships Contractor, Vietnam</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Ho Chi Minh</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>on_roll</t>
+          <t>short term</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -8730,44 +8730,44 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/feb33510-9ea7-4b69-b69d-87a41f7c2c2c</t>
+          <t>https://jobs.lever.co/spotify/d87833d0-fb78-4794-b45d-3fe5c8274bc8</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Non IT Purchase, Purchase</t>
+          <t>Music Business, Content</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:58.323463+00:00</t>
+          <t>2026-10-21T08:17:06.523867+00:00</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Spotify (Lever)</t>
+          <t>Meesho (Lever)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LEVER-SPOTIFY</t>
+          <t>LEVER-MEESHO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Art Director - Mexico</t>
+          <t>AM/ Manager - Risk &amp; Decision Science</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>permanent</t>
+          <t>full time employee</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -8789,44 +8789,44 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/223f9722-3579-4ff2-b123-e4cc7b0c1a64</t>
+          <t>https://jobs.lever.co/meesho/7d9af9b5-c1c7-48ec-bbb5-9b25e49f6596</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Marketing, Markets and Subscriber Growth</t>
+          <t>Financial Services, Financial Services</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:58.809110+00:00</t>
+          <t>2026-10-21T08:17:07.498211+00:00</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Spotify (Lever)</t>
+          <t>Meesho (Lever)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LEVER-SPOTIFY</t>
+          <t>LEVER-MEESHO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Artist &amp; Label Partnerships Contractor, Vietnam</t>
+          <t>AM/M - Risk Analytics - User Lending</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ho Chi Minh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>short term</t>
+          <t>full time employee</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -8848,44 +8848,44 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/spotify/d87833d0-fb78-4794-b45d-3fe5c8274bc8</t>
+          <t>https://jobs.lever.co/meesho/1969c4c1-fbcc-455a-850b-092d1d83eb2b</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Music Business, Content</t>
+          <t>Financial Services, Financial Services</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:58.809110+00:00</t>
+          <t>2026-10-21T08:17:07.498211+00:00</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Meesho (Lever)</t>
+          <t>Coupa Software (Lever)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LEVER-MEESHO</t>
+          <t>LEVER-COUPA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AM/ Manager - Risk &amp; Decision Science</t>
+          <t>Account Development Representative - 11887</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Coupa Software</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>full time employee</t>
+          <t>mid level</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -8907,44 +8907,44 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/7d9af9b5-c1c7-48ec-bbb5-9b25e49f6596</t>
+          <t>https://jobs.lever.co/coupa/d17fb20e-152c-4583-9add-c8bc779f658d</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Financial Services, Financial Services</t>
+          <t>Marketing, Marketing</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:59.385914+00:00</t>
+          <t>2026-10-21T08:17:10.123450+00:00</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Meesho (Lever)</t>
+          <t>Coupa Software (Lever)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LEVER-MEESHO</t>
+          <t>LEVER-COUPA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AM/M - Risk Analytics - User Lending</t>
+          <t>AVP - Enterprise</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>Coupa Software</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>full time employee</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -8966,44 +8966,44 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1969c4c1-fbcc-455a-850b-092d1d83eb2b</t>
+          <t>https://jobs.lever.co/coupa/56784094-c2cb-4eb4-b282-f700b4823d54</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Financial Services, Financial Services</t>
+          <t>Sales International, Sales</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-10-16T14:13:59.385914+00:00</t>
+          <t>2026-10-21T08:17:10.123450+00:00</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Coupa Software (Lever)</t>
+          <t>CRED (Lever)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LEVER-COUPA</t>
+          <t>LEVER-CRED</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Account Development Representative - 11887</t>
+          <t>accounts payable manager</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Coupa Software</t>
+          <t>CRED</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>hyderabad</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>mid level</t>
+          <t>full time</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -9025,44 +9025,44 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/coupa/d17fb20e-152c-4583-9add-c8bc779f658d</t>
+          <t>https://jobs.lever.co/cred/aa98a938-af3a-45f5-851d-966b2b5bad33</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Marketing, Marketing</t>
+          <t>finance, Prefr</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:18.822485+00:00</t>
+          <t>2026-10-21T08:17:10.413859+00:00</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Coupa Software (Lever)</t>
+          <t>CRED (Lever)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LEVER-COUPA</t>
+          <t>LEVER-CRED</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AVP - Enterprise</t>
+          <t>area collection manager east - recovery</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Coupa Software</t>
+          <t>CRED</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>executive</t>
+          <t>full time</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -9084,44 +9084,44 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/coupa/56784094-c2cb-4eb4-b282-f700b4823d54</t>
+          <t>https://jobs.lever.co/cred/76b5d976-5230-4939-b1ad-4b7d51a40396</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Sales International, Sales</t>
+          <t>collections, Prefr</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:18.822485+00:00</t>
+          <t>2026-10-21T08:17:10.413859+00:00</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRED (Lever)</t>
+          <t>Zomato (Lever)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LEVER-CRED</t>
+          <t>LEVER-ETERNAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>accounts payable manager</t>
+          <t>Performance Team - Open Interest - NYC</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CRED</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>hyderabad</t>
+          <t>New York City, NY</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9143,44 +9143,44 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/cred/aa98a938-af3a-45f5-851d-966b2b5bad33</t>
+          <t>https://jobs.lever.co/eternal/69e24776-7d20-4051-a03f-51a41aad53fa</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>finance, Prefr</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:19.256910+00:00</t>
+          <t>2026-10-21T08:17:11.242923+00:00</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRED (Lever)</t>
+          <t>Zomato (Lever)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LEVER-CRED</t>
+          <t>LEVER-ETERNAL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>business development &amp; partnerships</t>
+          <t>Performance Team - Open Interest - SF</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CRED</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>bengaluru</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9202,44 +9202,44 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/cred/09022710-e79a-4cf0-8060-df0e1cd64263</t>
+          <t>https://jobs.lever.co/eternal/7e299aed-d77b-4357-82dc-24e53917f920</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>consumer products, product &amp; growth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:19.256910+00:00</t>
+          <t>2026-10-21T08:17:11.243922+00:00</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Zomato (Lever)</t>
+          <t>Wealthfront (Lever)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LEVER-ETERNAL</t>
+          <t>LEVER-WEALTHFRONT</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Performance Team - Open Interest - NYC</t>
+          <t>Android Engineer</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Zomato</t>
+          <t>Wealthfront</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>New York City, NY</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>full time</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -9261,44 +9261,44 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/eternal/69e24776-7d20-4051-a03f-51a41aad53fa</t>
+          <t>https://jobs.lever.co/wealthfront/78d6f6d5-1f08-4d5d-87be-c4250567bfb5</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Engineering - Android, Engineering</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:23.265872+00:00</t>
+          <t>2026-10-21T08:17:11.642119+00:00</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Zomato (Lever)</t>
+          <t>Wealthfront (Lever)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>LEVER-ETERNAL</t>
+          <t>LEVER-WEALTHFRONT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Performance Team - Open Interest - SF</t>
+          <t>Anti-Money Laundering Monitoring Analyst</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Zomato</t>
+          <t>Wealthfront</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Palo Alto, San Francisco, New York City, or Seattle</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>full time</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -9320,44 +9320,44 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/eternal/7e299aed-d77b-4357-82dc-24e53917f920</t>
+          <t>https://jobs.lever.co/wealthfront/26d453d0-f9df-4396-a655-70f6dbceb328</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Compliance, Legal and Compliance</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:23.265872+00:00</t>
+          <t>2026-10-21T08:17:11.642119+00:00</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Wealthfront (Lever)</t>
+          <t>Gopuff (Lever)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>LEVER-WEALTHFRONT</t>
+          <t>LEVER-GOPUFF</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Android Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Wealthfront</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>full time</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -9379,54 +9379,54 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/wealthfront/78d6f6d5-1f08-4d5d-87be-c4250567bfb5</t>
+          <t>https://jobs.lever.co/gopuff/bfa7bc15-793e-486c-a3f5-b27d84c53025</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Engineering - Android, Engineering</t>
+          <t>Data &amp; Analytics, Tech, Product, &amp; Design</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:23.937652+00:00</t>
+          <t>2026-10-21T08:17:14.713962+00:00</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Wealthfront (Lever)</t>
+          <t>Gopuff (Lever)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LEVER-WEALTHFRONT</t>
+          <t>LEVER-GOPUFF</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Anti-Money Laundering Monitoring Analyst</t>
+          <t>Associate Category Manager</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Wealthfront</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Palo Alto, CA (Open to US-based Remote)</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>full time</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -9438,44 +9438,44 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/wealthfront/26d453d0-f9df-4396-a655-70f6dbceb328</t>
+          <t>https://jobs.lever.co/gopuff/49a77ebe-3d57-4766-8619-87ab738165d2</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Compliance, Legal and Compliance</t>
+          <t>Merchandising, Merchandising</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:23.937652+00:00</t>
+          <t>2026-10-21T08:17:14.713962+00:00</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Gopuff (Lever)</t>
+          <t>OpenAI (Ashby)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LEVER-GOPUFF</t>
+          <t>ASHBY-OPENAI</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Technical Program Manager, Compute Infrastructure</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>full time</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -9497,44 +9497,44 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/gopuff/bfa7bc15-793e-486c-a3f5-b27d84c53025</t>
+          <t>https://jobs.ashbyhq.com/openai/8fb1615c-34bf-47c4-a1d1-b7b2f836bbd3/application</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics, Tech, Product, &amp; Design</t>
+          <t>Technical Program Management, Technical Program Management</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:26.889022+00:00</t>
+          <t>2026-10-21T08:17:23.919174+00:00</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Gopuff (Lever)</t>
+          <t>OpenAI (Ashby)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LEVER-GOPUFF</t>
+          <t>ASHBY-OPENAI</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Associate Category Manager</t>
+          <t>Research Engineer</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>full time</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -9556,44 +9556,44 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/gopuff/49a77ebe-3d57-4766-8619-87ab738165d2</t>
+          <t>https://jobs.ashbyhq.com/openai/240d459b-696d-43eb-8497-fab3e56ecd9b/application</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Merchandising, Merchandising</t>
+          <t>Research, Research</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:26.889022+00:00</t>
+          <t>2026-10-21T08:17:23.919174+00:00</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OpenAI (Ashby)</t>
+          <t>Snowflake (Ashby)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ASHBY-OPENAI</t>
+          <t>ASHBY-SNOWFLAKE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Technical Program Manager, Compute Infrastructure</t>
+          <t>Lead, Strategic Finance - Deals (International)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>GB-London</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9615,44 +9615,44 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/8fb1615c-34bf-47c4-a1d1-b7b2f836bbd3/application</t>
+          <t>https://jobs.ashbyhq.com/snowflake/479e06f1-273d-4a1b-af56-6543761ebd75/application</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Technical Program Management, Technical Program Management</t>
+          <t>Finance, Finance</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:32.763844+00:00</t>
+          <t>2026-10-21T08:17:24.428289+00:00</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OpenAI (Ashby)</t>
+          <t>Snowflake (Ashby)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ASHBY-OPENAI</t>
+          <t>ASHBY-SNOWFLAKE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Research Engineer</t>
+          <t>Software Engineer - Database Engineering</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>US-CA-Menlo Park</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9674,49 +9674,49 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/240d459b-696d-43eb-8497-fab3e56ecd9b/application</t>
+          <t>https://jobs.ashbyhq.com/snowflake/db1375f0-ea5d-404a-b640-259f94dbc995/application</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Research, Research</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:32.763844+00:00</t>
+          <t>2026-10-21T08:17:24.428289+00:00</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Snowflake (Ashby)</t>
+          <t>Ramp (Ashby)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ASHBY-SNOWFLAKE</t>
+          <t>ASHBY-RAMP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Lead, Strategic Finance - Deals (International)</t>
+          <t>Security Engineer, Cloud</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>GB-London</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9733,49 +9733,49 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/479e06f1-273d-4a1b-af56-6543761ebd75/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/34413f8d-26bf-4bbc-8ade-eb309a0e2245/application</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Finance, Finance</t>
+          <t>Engineering, Backend</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:33.362560+00:00</t>
+          <t>2026-10-21T08:17:24.607015+00:00</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Snowflake (Ashby)</t>
+          <t>Ramp (Ashby)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ASHBY-SNOWFLAKE</t>
+          <t>ASHBY-RAMP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Software Engineer - Database Engineering</t>
+          <t>Mobile Engineer, Android</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>US-CA-Menlo Park</t>
+          <t>New York, NY (HQ)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9792,44 +9792,44 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/db1375f0-ea5d-404a-b640-259f94dbc995/application</t>
+          <t>https://jobs.ashbyhq.com/ramp/f564dcf9-9390-4a3f-896f-8047a5086040/application</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Engineering, Mobile</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:33.362560+00:00</t>
+          <t>2026-10-21T08:17:24.607015+00:00</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ramp (Ashby)</t>
+          <t>ElevenLabs (Ashby)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ASHBY-RAMP</t>
+          <t>ASHBY-ELEVENLABS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Security Engineer, Cloud</t>
+          <t>Account Manager - India</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9851,44 +9851,44 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/34413f8d-26bf-4bbc-8ade-eb309a0e2245/application</t>
+          <t>https://jobs.ashbyhq.com/elevenlabs/a571b8e4-8176-4e31-aab6-2287ee810236/application</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Engineering, Backend</t>
+          <t>Revenue, Revenue - India</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:33.763231+00:00</t>
+          <t>2026-10-21T08:17:25.081893+00:00</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ramp (Ashby)</t>
+          <t>ElevenLabs (Ashby)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ASHBY-RAMP</t>
+          <t>ASHBY-ELEVENLABS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mobile Engineer, Android</t>
+          <t>Enterprise Solutions Engineer - USA</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>New York, NY (HQ)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -9910,49 +9910,49 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/ramp/f564dcf9-9390-4a3f-896f-8047a5086040/application</t>
+          <t>https://jobs.ashbyhq.com/elevenlabs/275f43d0-b62d-401d-830c-7c1ac0e688aa/application</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Engineering, Mobile</t>
+          <t>Engineering &amp; Product, Enterprise - Deployment</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:33.763231+00:00</t>
+          <t>2026-10-21T08:17:25.081893+00:00</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ElevenLabs (Ashby)</t>
+          <t>Cursor (Anysphere) (Ashby)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ASHBY-ELEVENLABS</t>
+          <t>ASHBY-CURSOR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Account Manager - India</t>
+          <t>Software Engineer, Growth</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9969,49 +9969,49 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/elevenlabs/a571b8e4-8176-4e31-aab6-2287ee810236/application</t>
+          <t>https://jobs.ashbyhq.com/cursor/0ec39ed7-a5dc-4551-bb26-b7f4f9fb4a74/application</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Revenue, Revenue - India</t>
+          <t>Engineering, Teams</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:34.005025+00:00</t>
+          <t>2026-10-21T08:17:25.572515+00:00</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ElevenLabs (Ashby)</t>
+          <t>Cursor (Anysphere) (Ashby)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ASHBY-ELEVENLABS</t>
+          <t>ASHBY-CURSOR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Enterprise Solutions Engineer - USA</t>
+          <t>Software Engineer, RL Data</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Cursor (Anysphere)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10028,39 +10028,39 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/elevenlabs/275f43d0-b62d-401d-830c-7c1ac0e688aa/application</t>
+          <t>https://jobs.ashbyhq.com/cursor/aef8f0e7-37cd-4d6e-96c9-3af72f588bae/application</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Engineering &amp; Product, Enterprise - Deployment</t>
+          <t>Engineering, Machine Learning</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:34.005025+00:00</t>
+          <t>2026-10-21T08:17:25.572515+00:00</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere) (Ashby)</t>
+          <t>Perplexity AI (Ashby)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ASHBY-CURSOR</t>
+          <t>ASHBY-PERPLEXITY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Software Engineer, Growth</t>
+          <t>Product Marketing Manager, Partnerships</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -10087,39 +10087,39 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/cursor/0ec39ed7-a5dc-4551-bb26-b7f4f9fb4a74/application</t>
+          <t>https://jobs.ashbyhq.com/perplexity/d5bc2302-202f-4596-9c4d-8720d1e79064/application</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Engineering, Teams</t>
+          <t>Marketing &amp; Communications, Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:34.739652+00:00</t>
+          <t>2026-10-21T08:17:26.699188+00:00</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere) (Ashby)</t>
+          <t>Perplexity AI (Ashby)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ASHBY-CURSOR</t>
+          <t>ASHBY-PERPLEXITY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Software Engineer, RL Data</t>
+          <t>Member of Technical Staff (Software Engineer, Monetization)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cursor (Anysphere)</t>
+          <t>Perplexity AI</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10146,44 +10146,44 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/cursor/aef8f0e7-37cd-4d6e-96c9-3af72f588bae/application</t>
+          <t>https://jobs.ashbyhq.com/perplexity/043d6a58-87a1-4e3c-bf47-4dc351b94cf4/application</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Engineering, Machine Learning</t>
+          <t>AI Products, AI Products</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:34.740653+00:00</t>
+          <t>2026-10-21T08:17:26.699188+00:00</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Perplexity AI (Ashby)</t>
+          <t>Supabase (Ashby)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ASHBY-PERPLEXITY</t>
+          <t>ASHBY-SUPABASE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, Partnerships</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Perplexity AI</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Remote, Global</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10205,49 +10205,49 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/perplexity/d5bc2302-202f-4596-9c4d-8720d1e79064/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/3b5d54ca-741b-45ac-bd3f-31605a0d3541/application</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Marketing &amp; Communications, Marketing &amp; Communications</t>
+          <t>Business Operations, Business Operations</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:35.001949+00:00</t>
+          <t>2026-10-21T08:17:26.773202+00:00</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Perplexity AI (Ashby)</t>
+          <t>Supabase (Ashby)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ASHBY-PERPLEXITY</t>
+          <t>ASHBY-SUPABASE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Member of Technical Staff (Software Engineer, Monetization)</t>
+          <t>Customer Solution Architect (AMER)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Perplexity AI</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Remote, AMER</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10264,44 +10264,44 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/perplexity/043d6a58-87a1-4e3c-bf47-4dc351b94cf4/application</t>
+          <t>https://jobs.ashbyhq.com/supabase/d5573afa-636c-4219-832f-386f498243bf/application</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>AI Products, AI Products</t>
+          <t>Success, Success</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:35.001949+00:00</t>
+          <t>2026-10-21T08:17:26.773202+00:00</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Supabase (Ashby)</t>
+          <t>Synthesia (Ashby)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ASHBY-SUPABASE</t>
+          <t>ASHBY-SYNTHESIA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>SecOps Security Engineer (Staff-level, L6)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Synthesia</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Remote, Global</t>
+          <t>US Remote</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10323,44 +10323,44 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/3b5d54ca-741b-45ac-bd3f-31605a0d3541/application</t>
+          <t>https://jobs.ashbyhq.com/synthesia/c3c79cb1-3ead-46ac-abf2-04502e4655bd/application</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Business Operations, Business Operations</t>
+          <t>Engineering, Engineering - Security</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:35.458599+00:00</t>
+          <t>2026-10-21T08:17:27.465395+00:00</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Supabase (Ashby)</t>
+          <t>Synthesia (Ashby)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ASHBY-SUPABASE</t>
+          <t>ASHBY-SYNTHESIA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Customer Solution Architect (AMER)</t>
+          <t>Enterprise Account Executive</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>Synthesia</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Remote, AMER</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10382,54 +10382,54 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/d5573afa-636c-4219-832f-386f498243bf/application</t>
+          <t>https://jobs.ashbyhq.com/synthesia/11cac93d-fea6-4f22-add1-d4e3bb904b94/application</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Success, Success</t>
+          <t>Commercial, Enterprise Sales</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:35.458599+00:00</t>
+          <t>2026-10-21T08:17:27.465395+00:00</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Synthesia (Ashby)</t>
+          <t>Atlys (Ashby)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ASHBY-SYNTHESIA</t>
+          <t>ASHBY-ATLYS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SecOps Security Engineer (Staff-level, L6)</t>
+          <t>Fulfilment Intern</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Synthesia</t>
+          <t>Atlys</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>US Remote</t>
+          <t>Delhi HQ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -10441,44 +10441,44 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/synthesia/c3c79cb1-3ead-46ac-abf2-04502e4655bd/application</t>
+          <t>https://jobs.ashbyhq.com/atlys/b64524ad-e4ab-4e0f-b4fe-f13ffc661a92/application</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Engineering, Engineering - Security</t>
+          <t xml:space="preserve">Fulfilment , Fulfilment </t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36.211019+00:00</t>
+          <t>2026-10-21T08:17:27.945968+00:00</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Synthesia (Ashby)</t>
+          <t>Atlys (Ashby)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ASHBY-SYNTHESIA</t>
+          <t>ASHBY-ATLYS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive</t>
+          <t>City Scout - Vienna</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Synthesia</t>
+          <t>Atlys</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -10500,49 +10500,49 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/synthesia/11cac93d-fea6-4f22-add1-d4e3bb904b94/application</t>
+          <t>https://jobs.ashbyhq.com/atlys/bcaa129b-5708-4feb-8bb9-a00f3861002b/application</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Commercial, Enterprise Sales</t>
+          <t xml:space="preserve">Growth , Growth </t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36.211019+00:00</t>
+          <t>2026-10-21T08:17:27.945968+00:00</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Atlys (Ashby)</t>
+          <t>Linear (Ashby)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ASHBY-ATLYS</t>
+          <t>ASHBY-LINEAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Motion Designer</t>
+          <t>Senior / Staff Fullstack Engineer</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Atlys</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Delhi HQ</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10559,54 +10559,54 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlys/c9b3bf73-e663-46f8-a840-3a9f2e649fb2/application</t>
+          <t>https://jobs.ashbyhq.com/linear/d3bc1ced-3ce4-4086-a050-555055dbb1ff/application</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product , Product </t>
+          <t>Product, Engineering</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36.725446+00:00</t>
+          <t>2026-10-21T08:17:28.270773+00:00</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Atlys (Ashby)</t>
+          <t>Linear (Ashby)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ASHBY-ATLYS</t>
+          <t>ASHBY-LINEAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Fulfilment Intern</t>
+          <t>Senior / Staff Fullstack Engineer</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Atlys</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Delhi HQ</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>intern</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -10618,44 +10618,44 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlys/b64524ad-e4ab-4e0f-b4fe-f13ffc661a92/application</t>
+          <t>https://jobs.ashbyhq.com/linear/cd5ae036-0223-427a-b038-ba16ef9dcb32/application</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fulfilment , Fulfilment </t>
+          <t>Product, Engineering</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36.725446+00:00</t>
+          <t>2026-10-21T08:17:28.270773+00:00</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Linear (Ashby)</t>
+          <t>PostHog (Ashby)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ASHBY-LINEAR</t>
+          <t>ASHBY-POSTHOG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Senior / Staff Fullstack Engineer</t>
+          <t>Technical Customer Success Manager - EMEA</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>PostHog</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Remote (EMEA)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10677,44 +10677,44 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/d3bc1ced-3ce4-4086-a050-555055dbb1ff/application</t>
+          <t>https://jobs.ashbyhq.com/posthog/0be1b52c-2401-4ae2-b7fc-5d018c1ff96f/application</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Product, Engineering</t>
+          <t>Sales &amp; Customer Success, Customer Success</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36.975237+00:00</t>
+          <t>2026-10-21T08:17:28.756282+00:00</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Linear (Ashby)</t>
+          <t>PostHog (Ashby)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ASHBY-LINEAR</t>
+          <t>ASHBY-POSTHOG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Senior / Staff Fullstack Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>PostHog</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>North America</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10736,44 +10736,44 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/linear/cd5ae036-0223-427a-b038-ba16ef9dcb32/application</t>
+          <t>https://jobs.ashbyhq.com/posthog/20ab9628-20ff-4ae3-bd6a-46ae7e9dc6b8/application</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Product, Engineering</t>
+          <t>Engineering, Product Engineering</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:36.975237+00:00</t>
+          <t>2026-10-21T08:17:28.756282+00:00</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PostHog (Ashby)</t>
+          <t>Railway (Ashby)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ASHBY-POSTHOG</t>
+          <t>ASHBY-RAILWAY</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Technical Customer Success Manager - EMEA</t>
+          <t>Senior Full-Stack Engineer - Product</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PostHog</t>
+          <t>Railway</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Remote (EMEA)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10795,44 +10795,44 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/posthog/0be1b52c-2401-4ae2-b7fc-5d018c1ff96f/application</t>
+          <t>https://jobs.ashbyhq.com/railway/6ddcfe47-6cce-469b-ba6d-4f0e83440c9d/application</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success, Customer Success</t>
+          <t>Product, Engineering</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:37.459172+00:00</t>
+          <t>2026-10-21T08:17:29.443087+00:00</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PostHog (Ashby)</t>
+          <t>Railway (Ashby)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ASHBY-POSTHOG</t>
+          <t>ASHBY-RAILWAY</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>PostHog</t>
+          <t>Railway</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10854,49 +10854,49 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/posthog/20ab9628-20ff-4ae3-bd6a-46ae7e9dc6b8/application</t>
+          <t>https://jobs.ashbyhq.com/railway/b8072f95-043f-404d-a313-f0bdf8dd3c81/application</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Engineering, Product Engineering</t>
+          <t>Platform, Platform</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:37.459172+00:00</t>
+          <t>2026-10-21T08:17:29.443087+00:00</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Railway (Ashby)</t>
+          <t>Cognition (Devin) (Ashby)</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ASHBY-RAILWAY</t>
+          <t>ASHBY-COGNITION</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer - Product</t>
+          <t>General Application - Cognition</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Railway</t>
+          <t>Cognition (Devin)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -10913,49 +10913,49 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/railway/6ddcfe47-6cce-469b-ba6d-4f0e83440c9d/application</t>
+          <t>https://jobs.ashbyhq.com/cognition/4841bda0-057a-4471-801f-70309c3c02d5/application</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Product, Engineering</t>
+          <t>General &amp; Administrative, General &amp; Administrative</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:38.207652+00:00</t>
+          <t>2026-10-21T08:17:30.008152+00:00</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Railway (Ashby)</t>
+          <t>Cognition (Devin) (Ashby)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ASHBY-RAILWAY</t>
+          <t>ASHBY-COGNITION</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Research Engineer, Post-Training</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Railway</t>
+          <t>Cognition (Devin)</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10972,39 +10972,39 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/railway/b8072f95-043f-404d-a313-f0bdf8dd3c81/application</t>
+          <t>https://jobs.ashbyhq.com/cognition/72d3db28-07d3-4c28-b49f-1bdf6e8e0f10/application</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Platform, Platform</t>
+          <t>Research &amp; Development, Research</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:38.208690+00:00</t>
+          <t>2026-10-21T08:17:30.008152+00:00</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Cognition (Devin) (Ashby)</t>
+          <t>Harvey AI (Ashby)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ASHBY-COGNITION</t>
+          <t>ASHBY-HARVEY</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>General Application - Cognition</t>
+          <t>Legal Engineering Manager (Law Firm, Litigation/Regulatory)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Cognition (Devin)</t>
+          <t>Harvey AI</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11031,49 +11031,49 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/cognition/4841bda0-057a-4471-801f-70309c3c02d5/application</t>
+          <t>https://jobs.ashbyhq.com/harvey/977e6184-2dc4-422b-8ab3-bc26bb73f778/application</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>General &amp; Administrative, General &amp; Administrative</t>
+          <t>Go to Market, Go to Market</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:38.536531+00:00</t>
+          <t>2026-10-21T08:17:30.664698+00:00</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Cognition (Devin) (Ashby)</t>
+          <t>Harvey AI (Ashby)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ASHBY-COGNITION</t>
+          <t>ASHBY-HARVEY</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Research Engineer, Post-Training</t>
+          <t>Customer Success Manager, Mid Market, EMEA</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Cognition (Devin)</t>
+          <t>Harvey AI</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11090,44 +11090,44 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/cognition/72d3db28-07d3-4c28-b49f-1bdf6e8e0f10/application</t>
+          <t>https://jobs.ashbyhq.com/harvey/e04146f6-f79a-4023-9523-fe691038b330/application</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Research &amp; Development, Research</t>
+          <t>Customer Success, Customer Success</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:38.536531+00:00</t>
+          <t>2026-10-21T08:17:30.664698+00:00</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Harvey AI (Ashby)</t>
+          <t>LangChain (Ashby)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ASHBY-HARVEY</t>
+          <t>ASHBY-LANGCHAIN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Legal Engineering Manager (Law Firm, Litigation/Regulatory)</t>
+          <t>Python OSS Engineer</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Harvey AI</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11149,49 +11149,49 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/harvey/977e6184-2dc4-422b-8ab3-bc26bb73f778/application</t>
+          <t>https://jobs.ashbyhq.com/langchain/74e5f9f4-e44a-4594-ba26-abdf71bf287d/application</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Go to Market, Go to Market</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:39.130486+00:00</t>
+          <t>2026-10-21T08:17:30.996504+00:00</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Harvey AI (Ashby)</t>
+          <t>LangChain (Ashby)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ASHBY-HARVEY</t>
+          <t>ASHBY-LANGCHAIN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Customer Success Manager, Mid Market, EMEA</t>
+          <t>Enterprise Account Executive (San Francisco Bay Area)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Harvey AI</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -11208,44 +11208,44 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/harvey/e04146f6-f79a-4023-9523-fe691038b330/application</t>
+          <t>https://jobs.ashbyhq.com/langchain/9930dd01-d12e-42e1-b751-5240c3814f85/application</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Customer Success, Customer Success</t>
+          <t>Sales, Sales</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:39.130486+00:00</t>
+          <t>2026-10-21T08:17:30.996504+00:00</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LangChain (Ashby)</t>
+          <t>Modal Labs (Ashby)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ASHBY-LANGCHAIN</t>
+          <t>ASHBY-MODAL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Python OSS Engineer</t>
+          <t>Member of Technical Staff - Systems</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Modal Labs</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/langchain/74e5f9f4-e44a-4594-ba26-abdf71bf287d/application</t>
+          <t>https://jobs.ashbyhq.com/modal/9b33ebe7-e829-4f03-97ba-5c94dbd7daf6/application</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11277,34 +11277,34 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:39.521486+00:00</t>
+          <t>2026-10-21T08:17:31.471241+00:00</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LangChain (Ashby)</t>
+          <t>Modal Labs (Ashby)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ASHBY-LANGCHAIN</t>
+          <t>ASHBY-MODAL</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive (San Francisco Bay Area)</t>
+          <t>Forward Deployed Engineer - ML</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Modal Labs</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11326,44 +11326,44 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/langchain/9930dd01-d12e-42e1-b751-5240c3814f85/application</t>
+          <t>https://jobs.ashbyhq.com/modal/9fadb51f-ce11-41b1-84d5-470e66cc8ee9/application</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Sales, Sales</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:39.521486+00:00</t>
+          <t>2026-10-21T08:17:31.472240+00:00</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Modal Labs (Ashby)</t>
+          <t>Lovable (Ashby)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ASHBY-MODAL</t>
+          <t>ASHBY-LOVABLE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Member of Technical Staff - Systems</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Modal Labs</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11385,44 +11385,44 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/modal/9b33ebe7-e829-4f03-97ba-5c94dbd7daf6/application</t>
+          <t>https://jobs.ashbyhq.com/lovable/cfef6fe1-e0c9-4139-8618-b51bfb1dc683/application</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>EPD, Data &amp; Insights</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:40.011814+00:00</t>
+          <t>2026-10-21T08:17:31.818300+00:00</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Modal Labs (Ashby)</t>
+          <t>Lovable (Ashby)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ASHBY-MODAL</t>
+          <t>ASHBY-LOVABLE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - ML</t>
+          <t>Research Engineering Lead</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Modal Labs</t>
+          <t>Lovable</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11444,49 +11444,49 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/modal/9fadb51f-ce11-41b1-84d5-470e66cc8ee9/application</t>
+          <t>https://jobs.ashbyhq.com/lovable/79e04665-0e50-45f8-92e3-9237bcb4e0bc/application</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>EPD, Engineering</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:40.011814+00:00</t>
+          <t>2026-10-21T08:17:31.818300+00:00</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Lovable (Ashby)</t>
+          <t>Pika (Ashby)</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ASHBY-LOVABLE</t>
+          <t>ASHBY-PIKA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Data Platform/Infrastructure Engineer</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>US remote</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11503,49 +11503,49 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/lovable/cfef6fe1-e0c9-4139-8618-b51bfb1dc683/application</t>
+          <t>https://jobs.ashbyhq.com/pika/cc4dffe4-2cad-4287-a28b-b875ee35b541/application</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>EPD, Data &amp; Insights</t>
+          <t>Creative, Creative</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:40.535387+00:00</t>
+          <t>2026-10-21T08:17:32.474752+00:00</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Lovable (Ashby)</t>
+          <t>Pika (Ashby)</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ASHBY-LOVABLE</t>
+          <t>ASHBY-PIKA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Research Engineering Lead</t>
+          <t>Research Scientist, Post-Training — Video Generation</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Lovable</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>US remote</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11562,49 +11562,49 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/lovable/79e04665-0e50-45f8-92e3-9237bcb4e0bc/application</t>
+          <t>https://jobs.ashbyhq.com/pika/d3993c91-4dd5-4868-8108-4e9b78133e7b/application</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>EPD, Engineering</t>
+          <t>Research, Research</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:40.535387+00:00</t>
+          <t>2026-10-21T08:17:32.474752+00:00</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Pika (Ashby)</t>
+          <t>Braintrust (Ashby)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ASHBY-PIKA</t>
+          <t>ASHBY-BRAINTRUST</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Software Engineer, Systems</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Braintrust</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>US remote</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11621,49 +11621,49 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/pika/cc4dffe4-2cad-4287-a28b-b875ee35b541/application</t>
+          <t>https://jobs.ashbyhq.com/braintrust/8b9cfa26-627f-442c-a358-783b0e4ef930/application</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Creative, Creative</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:41.015243+00:00</t>
+          <t>2026-10-21T08:17:33.004463+00:00</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Pika (Ashby)</t>
+          <t>Braintrust (Ashby)</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ASHBY-PIKA</t>
+          <t>ASHBY-BRAINTRUST</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Research Scientist, Post-Training — Video Generation</t>
+          <t>Software Engineer, Product</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Braintrust</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>US remote</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11680,44 +11680,44 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/pika/d3993c91-4dd5-4868-8108-4e9b78133e7b/application</t>
+          <t>https://jobs.ashbyhq.com/braintrust/7d0a5b62-a554-48f0-b2f7-8cbac0e98ae6/application</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Research, Research</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:41.015243+00:00</t>
+          <t>2026-10-21T08:17:33.004463+00:00</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Braintrust (Ashby)</t>
+          <t>Dust (Ashby)</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ASHBY-BRAINTRUST</t>
+          <t>ASHBY-DUST</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems</t>
+          <t>Partner Development Manager</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Braintrust</t>
+          <t>Dust</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -11739,44 +11739,44 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/braintrust/8b9cfa26-627f-442c-a358-783b0e4ef930/application</t>
+          <t>https://jobs.ashbyhq.com/dust/58b990de-e5a2-4e60-ab42-f76b67b11183/application</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Ecosystem, Partnerships</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:41.765514+00:00</t>
+          <t>2026-10-21T08:17:33.532752+00:00</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Braintrust (Ashby)</t>
+          <t>Dust (Ashby)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ASHBY-BRAINTRUST</t>
+          <t>ASHBY-DUST</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Software Engineer, Product</t>
+          <t>Field Marketing Specialist</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Braintrust</t>
+          <t>Dust</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11798,49 +11798,49 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/braintrust/7d0a5b62-a554-48f0-b2f7-8cbac0e98ae6/application</t>
+          <t>https://jobs.ashbyhq.com/dust/a5e1d600-05dd-4e17-96b0-a5f629d5ad11/application</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Awareness, Marketing</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:41.765514+00:00</t>
+          <t>2026-10-21T08:17:33.532752+00:00</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Dust (Ashby)</t>
+          <t>Baseten (Ashby)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ASHBY-DUST</t>
+          <t>ASHBY-BASETEN</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Partner Development Manager</t>
+          <t>Software Engineer - Dedicated Inference</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Dust</t>
+          <t>Baseten</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -11857,49 +11857,49 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/dust/58b990de-e5a2-4e60-ab42-f76b67b11183/application</t>
+          <t>https://jobs.ashbyhq.com/baseten/fc6e5f2e-eb2d-4a6c-8a51-8422e8662bde/application</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Ecosystem, Partnerships</t>
+          <t>EPD, Dedicated Inference</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:42.307411+00:00</t>
+          <t>2026-10-21T08:17:33.872886+00:00</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Dust (Ashby)</t>
+          <t>Baseten (Ashby)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ASHBY-DUST</t>
+          <t>ASHBY-BASETEN</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Field Marketing Specialist</t>
+          <t>Account Executive - AI Native</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Dust</t>
+          <t>Baseten</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11916,44 +11916,44 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/dust/a5e1d600-05dd-4e17-96b0-a5f629d5ad11/application</t>
+          <t>https://jobs.ashbyhq.com/baseten/df2f0ebb-a84a-45c2-bc74-dc9589fcc1ae/application</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Awareness, Marketing</t>
+          <t>GTM, AI Native</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:42.307411+00:00</t>
+          <t>2026-10-21T08:17:33.873886+00:00</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Baseten (Ashby)</t>
+          <t>Cohere (Ashby)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ASHBY-BASETEN</t>
+          <t>ASHBY-COHERE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Software Engineer - Dedicated Inference</t>
+          <t>Senior Full-Stack Engineer, Internal Applications</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Baseten</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11975,44 +11975,44 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/baseten/fc6e5f2e-eb2d-4a6c-8a51-8422e8662bde/application</t>
+          <t>https://jobs.ashbyhq.com/cohere/7133d205-5421-4336-a8e2-6037b5f55073/application</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>EPD, Dedicated Inference</t>
+          <t>Engineering &amp; Infra, Internal Applications</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:42.843719+00:00</t>
+          <t>2026-10-21T08:17:34.402661+00:00</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Baseten (Ashby)</t>
+          <t>Cohere (Ashby)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ASHBY-BASETEN</t>
+          <t>ASHBY-COHERE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Account Executive - AI Native</t>
+          <t>Member of Technical Staff, Modeling</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Baseten</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -12034,49 +12034,49 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/baseten/df2f0ebb-a84a-45c2-bc74-dc9589fcc1ae/application</t>
+          <t>https://jobs.ashbyhq.com/cohere/3136a5a5-06fd-4c82-8b72-a43467e6b128/application</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>GTM, AI Native</t>
+          <t>Modeling, Modeling</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:42.843719+00:00</t>
+          <t>2026-10-21T08:17:34.402661+00:00</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Cohere (Ashby)</t>
+          <t>Anyscale (Ashby)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ASHBY-COHERE</t>
+          <t>ASHBY-ANYSCALE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer, Internal Applications</t>
+          <t>Enterprise Account Executive</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Anyscale</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -12093,49 +12093,49 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/cohere/7133d205-5421-4336-a8e2-6037b5f55073/application</t>
+          <t>https://jobs.ashbyhq.com/anyscale/02698dc0-9416-425f-a13d-0938ffd229a8/application</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Engineering &amp; Infra, Internal Applications</t>
+          <t>Sales, Sales</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:43.118360+00:00</t>
+          <t>2026-10-21T08:17:34.836254+00:00</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Cohere (Ashby)</t>
+          <t>Anyscale (Ashby)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ASHBY-COHERE</t>
+          <t>ASHBY-ANYSCALE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Modeling</t>
+          <t>Software Engineer, Ray Core</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Anyscale</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Bengaluru, Karnataka</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12152,49 +12152,49 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/cohere/3136a5a5-06fd-4c82-8b72-a43467e6b128/application</t>
+          <t>https://jobs.ashbyhq.com/anyscale/8b29c5e5-d56f-4c52-8887-a6a1827cf042/application</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Modeling, Modeling</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:43.118360+00:00</t>
+          <t>2026-10-21T08:17:34.836254+00:00</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Anyscale (Ashby)</t>
+          <t>Lightning AI (Ashby)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ASHBY-ANYSCALE</t>
+          <t>ASHBY-LIGHTNING</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Enterprise Account Executive</t>
+          <t>Assets Protocol Engineer (Remote)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Anyscale</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Lightning Labs</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -12211,49 +12211,49 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/anyscale/02698dc0-9416-425f-a13d-0938ffd229a8/application</t>
+          <t>https://jobs.ashbyhq.com/lightning/67891b35-9bc4-4414-aa53-c0c2c4567d26/application</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Sales, Sales</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:43.787651+00:00</t>
+          <t>2026-10-21T08:17:35.530946+00:00</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Anyscale (Ashby)</t>
+          <t>Lightning AI (Ashby)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ASHBY-ANYSCALE</t>
+          <t>ASHBY-LIGHTNING</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Software Engineer, Ray Core</t>
+          <t>Platform Engineer (Remote)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Anyscale</t>
+          <t>Lightning AI</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka</t>
+          <t>Lightning Labs</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/anyscale/8b29c5e5-d56f-4c52-8887-a6a1827cf042/application</t>
+          <t>https://jobs.ashbyhq.com/lightning/fde1d2b6-99e1-404a-b343-c35b2c40f9ae/application</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12280,39 +12280,39 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:43.787651+00:00</t>
+          <t>2026-10-21T08:17:35.530946+00:00</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Lightning AI (Ashby)</t>
+          <t>Tldraw (Ashby)</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ASHBY-LIGHTNING</t>
+          <t>ASHBY-TLDRAW</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Assets Protocol Engineer (Remote)</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Lightning AI</t>
+          <t>Tldraw</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Lightning Labs</t>
+          <t>London Office</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -12329,44 +12329,44 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/lightning/67891b35-9bc4-4414-aa53-c0c2c4567d26/application</t>
+          <t>https://jobs.ashbyhq.com/tldraw/c52007ee-bac0-4176-a5f0-48fe6e1fe854/application</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Product &amp; Engineering, Product &amp; Engineering</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:44.301898+00:00</t>
+          <t>2026-10-21T08:17:36.211302+00:00</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Lightning AI (Ashby)</t>
+          <t>Resend (Ashby)</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ASHBY-LIGHTNING</t>
+          <t>ASHBY-RESEND</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote)</t>
+          <t>Security Engineer, Platform</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Lightning AI</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Lightning Labs</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/lightning/fde1d2b6-99e1-404a-b343-c35b2c40f9ae/application</t>
+          <t>https://jobs.ashbyhq.com/resend/cde17f7c-4c70-435f-be38-ef5abe94ff22/application</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12398,39 +12398,39 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:44.301898+00:00</t>
+          <t>2026-10-21T08:17:36.528309+00:00</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Tldraw (Ashby)</t>
+          <t>Resend (Ashby)</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ASHBY-TLDRAW</t>
+          <t>ASHBY-RESEND</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Backend Engineer, MTA</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Tldraw</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>London Office</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -12447,49 +12447,49 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/tldraw/c52007ee-bac0-4176-a5f0-48fe6e1fe854/application</t>
+          <t>https://jobs.ashbyhq.com/resend/053bde8f-294e-4cce-9d62-2301282120a2/application</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>Product &amp; Engineering, Product &amp; Engineering</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:44.818473+00:00</t>
+          <t>2026-10-21T08:17:36.528309+00:00</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Resend (Ashby)</t>
+          <t>Axiom (Ashby)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ASHBY-RESEND</t>
+          <t>ASHBY-AXIOM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Security Engineer, Platform</t>
+          <t>ZK Proof Engineer</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Axiom</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/resend/cde17f7c-4c70-435f-be38-ef5abe94ff22/application</t>
+          <t>https://jobs.ashbyhq.com/axiom/363ab5a7-499a-48b6-9ed1-ebb44df570a4/application</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12516,39 +12516,39 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:45.074262+00:00</t>
+          <t>2026-10-21T08:17:37.041761+00:00</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Resend (Ashby)</t>
+          <t>Axiom (Ashby)</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ASHBY-RESEND</t>
+          <t>ASHBY-AXIOM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Backend Engineer, MTA</t>
+          <t>Distributed Systems Engineer</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Axiom</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/resend/053bde8f-294e-4cce-9d62-2301282120a2/application</t>
+          <t>https://jobs.ashbyhq.com/axiom/3f411517-8eaa-4136-bd4e-9b342b3a79b6/application</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12575,34 +12575,34 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:45.074262+00:00</t>
+          <t>2026-10-21T08:17:37.041761+00:00</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Axiom (Ashby)</t>
+          <t>Neon (Ashby)</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ASHBY-AXIOM</t>
+          <t>ASHBY-NEON</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ZK Proof Engineer</t>
+          <t>Lead Product Marketing Manager</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Axiom</t>
+          <t>Neon</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -12624,44 +12624,44 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/axiom/363ab5a7-499a-48b6-9ed1-ebb44df570a4/application</t>
+          <t>https://jobs.ashbyhq.com/neon/ceeecef6-dce4-4d8f-aea9-c2ffb87c7a91/application</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Revenue, Revenue</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:45.827042+00:00</t>
+          <t>2026-10-21T08:17:37.540823+00:00</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Axiom (Ashby)</t>
+          <t>Neon (Ashby)</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ASHBY-AXIOM</t>
+          <t>ASHBY-NEON</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Distributed Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Axiom</t>
+          <t>Neon</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/axiom/3f411517-8eaa-4136-bd4e-9b342b3a79b6/application</t>
+          <t>https://jobs.ashbyhq.com/neon/86131334-4a12-4e86-8b53-d816519da8f3/application</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12693,39 +12693,39 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:45.827042+00:00</t>
+          <t>2026-10-21T08:17:37.540823+00:00</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Neon (Ashby)</t>
+          <t>Render (Ashby)</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ASHBY-NEON</t>
+          <t>ASHBY-RENDER</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lead Product Marketing Manager</t>
+          <t>Software Engineer, Product (all levels)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Remote: United States</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -12742,49 +12742,49 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/neon/ceeecef6-dce4-4d8f-aea9-c2ffb87c7a91/application</t>
+          <t>https://jobs.ashbyhq.com/render/c7d896f2-20a9-4b44-9f7d-13929a0fe453/application</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Revenue, Revenue</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:46.082133+00:00</t>
+          <t>2026-10-21T08:17:38.059419+00:00</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Neon (Ashby)</t>
+          <t>Render (Ashby)</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ASHBY-NEON</t>
+          <t>ASHBY-RENDER</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Security (all levels)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Remote: United States</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/neon/86131334-4a12-4e86-8b53-d816519da8f3/application</t>
+          <t>https://jobs.ashbyhq.com/render/226a1b3b-5937-4880-817b-4beb1f72ecc6/application</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12811,39 +12811,39 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:46.082133+00:00</t>
+          <t>2026-10-21T08:17:38.060418+00:00</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Render (Ashby)</t>
+          <t>Envoy (Ashby)</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ASHBY-RENDER</t>
+          <t>ASHBY-ENVOY</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Software Engineer, Product (all levels)</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Envoy</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Remote: United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12860,49 +12860,49 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/render/c7d896f2-20a9-4b44-9f7d-13929a0fe453/application</t>
+          <t>https://jobs.ashbyhq.com/envoy/3a2fb81f-f22a-459d-a246-5dd0126d3f1f/application</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Research &amp; Development, Design</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:46.858082+00:00</t>
+          <t>2026-10-21T08:17:38.565694+00:00</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Render (Ashby)</t>
+          <t>Envoy (Ashby)</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ASHBY-RENDER</t>
+          <t>ASHBY-ENVOY</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Software Engineer, Security (all levels)</t>
+          <t>Member of Technical Staff, Labs</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Envoy</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Remote: United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -12919,44 +12919,44 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/render/226a1b3b-5937-4880-817b-4beb1f72ecc6/application</t>
+          <t>https://jobs.ashbyhq.com/envoy/5499e5fa-3e9f-4722-a407-0325d14cef23/application</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Research &amp; Development, Engineering</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:46.858082+00:00</t>
+          <t>2026-10-21T08:17:38.565694+00:00</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Envoy (Ashby)</t>
+          <t>Plane (Ashby)</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ASHBY-ENVOY</t>
+          <t>ASHBY-PLANE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Product Marketing Manager</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Envoy</t>
+          <t>Plane</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -12978,44 +12978,44 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/envoy/3a2fb81f-f22a-459d-a246-5dd0126d3f1f/application</t>
+          <t>https://jobs.ashbyhq.com/plane/c1bd8436-d469-4d16-878c-2b41c8dfb82c/application</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>Research &amp; Development, Design</t>
+          <t>Go-To-Market (GTM), Marketing</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:47.107217+00:00</t>
+          <t>2026-10-21T08:17:39.054745+00:00</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Envoy (Ashby)</t>
+          <t>Plane (Ashby)</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ASHBY-ENVOY</t>
+          <t>ASHBY-PLANE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Member of Technical Staff, Labs</t>
+          <t>Software Engineer, Backend (Node.js)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Envoy</t>
+          <t>Plane</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13037,44 +13037,44 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/envoy/5499e5fa-3e9f-4722-a407-0325d14cef23/application</t>
+          <t>https://jobs.ashbyhq.com/plane/188f905e-3f6f-4569-9a32-d8ec48dfe656/application</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Research &amp; Development, Engineering</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:47.107217+00:00</t>
+          <t>2026-10-21T08:17:39.055792+00:00</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Plane (Ashby)</t>
+          <t>Twenty (Ashby)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ASHBY-PLANE</t>
+          <t>ASHBY-TWENTY</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Product Marketing Manager</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Plane</t>
+          <t>Twenty</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -13096,44 +13096,44 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/plane/c1bd8436-d469-4d16-878c-2b41c8dfb82c/application</t>
+          <t>https://jobs.ashbyhq.com/twenty/490ea911-5a82-449a-89ed-c40f2beff9d5/application</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>Go-To-Market (GTM), Marketing</t>
+          <t>Engineering, Sofware Engineering</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:47.856320+00:00</t>
+          <t>2026-10-21T08:17:39.564261+00:00</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Plane (Ashby)</t>
+          <t>Twenty (Ashby)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ASHBY-PLANE</t>
+          <t>ASHBY-TWENTY</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend (Node.js)</t>
+          <t>Staff Product Manager, Autonomous Cyber</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Plane</t>
+          <t>Twenty</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -13155,44 +13155,44 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/plane/188f905e-3f6f-4569-9a32-d8ec48dfe656/application</t>
+          <t>https://jobs.ashbyhq.com/twenty/3486ffc9-bd3e-4229-a649-b321694d9d57/application</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Engineering, Engineering</t>
+          <t>Product, Product Management</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:47.856320+00:00</t>
+          <t>2026-10-21T08:17:39.564261+00:00</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Twenty (Ashby)</t>
+          <t>Speakeasy (Ashby)</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ASHBY-TWENTY</t>
+          <t>ASHBY-SPEAKEASY</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Twenty</t>
+          <t>Speakeasy</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -13214,44 +13214,44 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/twenty/490ea911-5a82-449a-89ed-c40f2beff9d5/application</t>
+          <t>https://jobs.ashbyhq.com/speakeasy/def210b2-b6aa-421b-84c4-dcd278f95db9/application</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>Engineering, Sofware Engineering</t>
+          <t>Engineering, Engineering</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:48.362060+00:00</t>
+          <t>2026-10-21T08:17:40.074562+00:00</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Twenty (Ashby)</t>
+          <t>Speakeasy (Ashby)</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ASHBY-TWENTY</t>
+          <t>ASHBY-SPEAKEASY</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Staff Product Manager, Autonomous Cyber</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Twenty</t>
+          <t>Speakeasy</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -13273,44 +13273,44 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/twenty/3486ffc9-bd3e-4229-a649-b321694d9d57/application</t>
+          <t>https://jobs.ashbyhq.com/speakeasy/b0c122c2-f0db-46ed-8c43-7bb72a4638a0/application</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Product, Product Management</t>
+          <t>Go-to-market, Go-to-market</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:48.362060+00:00</t>
+          <t>2026-10-21T08:17:40.074562+00:00</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Speakeasy (Ashby)</t>
+          <t>Target (Workday)</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ASHBY-SPEAKEASY</t>
+          <t>WD-TARGET</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Sr Applied Data Scientist - 1:1 Personalization, Audience and Experimentation (applied ML, PyToch, A/B testing)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Speakeasy</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>7000 Target Pkwy N,NCD-0375 Brooklyn Park,MN 55445</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
@@ -13332,44 +13332,40 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/speakeasy/def210b2-b6aa-421b-84c4-dcd278f95db9/application</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>Engineering, Engineering</t>
-        </is>
-      </c>
+          <t>https://target.wd5.myworkdayjobs.com/job/7000-Target-Pkwy-NNCD-0375-Brooklyn-ParkMN-55445/Sr-Applied-Data-Scientist---1-1-Personalization--Audience-and-Experimentation--applied-ML--PyToch--A-B-testing-_R0000454434</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:48.842861+00:00</t>
+          <t>2026-10-21T08:17:47.143940+00:00</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Speakeasy (Ashby)</t>
+          <t>Target (Workday)</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ASHBY-SPEAKEASY</t>
+          <t>WD-TARGET</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Sr. Merchandise Planner Mobile Accessories (Minneapolis)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Speakeasy</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>1000 Nicollet Mall, Minneapolis,MN 55403-2542</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -13379,7 +13375,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -13391,44 +13387,40 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/speakeasy/b0c122c2-f0db-46ed-8c43-7bb72a4638a0/application</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>Go-to-market, Go-to-market</t>
-        </is>
-      </c>
+          <t>https://target.wd5.myworkdayjobs.com/job/1000-Nicollet-Mall-MinneapolisMN-55403-2542/Sr-Merchandise-Planner-Mobile-Accessories--Minneapolis-_R0000478229</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:48.842861+00:00</t>
+          <t>2026-10-21T08:17:47.143940+00:00</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Target (Workday)</t>
+          <t>Nvidia (Workday)</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>WD-TARGET</t>
+          <t>WD-NVIDIA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Full Time Hourly Warehouse Operations Hiring Overnight Shifts (T0551)</t>
+          <t>Physical Design, VLSI - New College Grad 2027</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1090 73rd Ave NE, Fridley,MN 55432-3407</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13450,40 +13442,40 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>https://target.wd5.myworkdayjobs.com/job/1090-73rd-Ave-NE-FridleyMN-55432-3407/Full-Time-Hourly-Warehouse-Operations-Openings-T0551-_R0000477041</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/job/China-Shanghai/Physical-Design--VLSI---New-College-Grad-2027_JR2024940</t>
         </is>
       </c>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:56.407730+00:00</t>
+          <t>2026-10-21T08:17:49.629106+00:00</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Target (Workday)</t>
+          <t>Nvidia (Workday)</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>WD-TARGET</t>
+          <t>WD-NVIDIA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Seasonal Full Time Hourly Warehouse Associate Openings Hiring Overnight Shifts (T3858)</t>
+          <t>Applied Research Intern, Integrated Sensing and Communications (ISAC)-NVIDIA Aerial - Summer 2027</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2700 Winter St NE, Minneapolis,MN 55413-2945</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13505,40 +13497,40 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>https://target.wd5.myworkdayjobs.com/job/2700-Winter-St-NE-MinneapolisMN-55413-2945/Seasonal-Full-Time-Hourly-Warehouse-Associate-Openings--T3858-_R0000447574</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/job/US-CA-Santa-Clara/Applied-Research-Intern--Integrated-Sensing-and-Communications--ISAC--NVIDIA-Aerial---Summer-2027_JR2028027</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:56.407730+00:00</t>
+          <t>2026-10-21T08:17:49.629106+00:00</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Nvidia (Workday)</t>
+          <t>Salesforce (Workday)</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>WD-NVIDIA</t>
+          <t>WD-SALESFORCE</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Robotics Simulation</t>
+          <t>Product Security Lead</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>Ireland - Dublin</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -13560,40 +13552,40 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/job/Canada-Toronto/Senior-DevOps-Engineer---Robotics-Simulation_JR2027642</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/job/Ireland---Dublin/Product-Security-Lead_JR364992</t>
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:58.797808+00:00</t>
+          <t>2026-10-21T08:17:51.107777+00:00</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Nvidia (Workday)</t>
+          <t>Salesforce (Workday)</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>WD-NVIDIA</t>
+          <t>WD-SALESFORCE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Senior Architect - Data Processing Systems, Analytics and Data Intelligence</t>
+          <t>Senior Technical Consultant - AI platform engineering and Salesforce project delivery</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>3 Locations</t>
+          <t>India - Bangalore</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -13615,40 +13607,40 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/job/US-CA-Santa-Clara/Senior-Architect---Data-Processing-Systems--Analytics-and-Data-Intelligence_JR2028088-1</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/job/India---Bangalore/Senior-Technical-Consultant---AI-platform-engineering-and-Salesforce-project-delivery_JR365157</t>
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2026-10-16T14:14:58.797808+00:00</t>
+          <t>2026-10-21T08:17:51.107777+00:00</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Salesforce (Workday)</t>
+          <t>Cisco (Workday)</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>WD-SALESFORCE</t>
+          <t>WD-CISCO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Manager, Strategic Finance Analytics</t>
+          <t>Software Engineer - Webex Web Clients</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Georgia - Atlanta</t>
+          <t>Bratislava, Slovakia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -13670,40 +13662,40 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>https://salesforce.wd12.myworkdayjobs.com/job/Georgia---Atlanta/Manager--Strategic-Finance-Analytics_JR362687</t>
+          <t>https://cisco.wd5.myworkdayjobs.com/job/Bratislava-Slovakia/Software-Engineer---Webex-Web-Clients_2028671</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:00.262338+00:00</t>
+          <t>2026-10-21T08:17:52.237698+00:00</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Salesforce (Workday)</t>
+          <t>Cisco (Workday)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>WD-SALESFORCE</t>
+          <t>WD-CISCO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant — Salesforce DevOps</t>
+          <t>Chief of Staff</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>San Jose, California, US</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -13725,40 +13717,40 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>https://salesforce.wd12.myworkdayjobs.com/job/India---Bangalore/Senior-Technical-Consultant---Salesforce-DevOps_JR347675</t>
+          <t>https://cisco.wd5.myworkdayjobs.com/job/San-Jose-California-US/Chief-of-Staff_2028387</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:00.262338+00:00</t>
+          <t>2026-10-21T08:17:52.237698+00:00</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Cisco (Workday)</t>
+          <t>Intel (Workday)</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>WD-CISCO</t>
+          <t>WD-INTEL</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Webex Web Client</t>
+          <t>Senior Member of Technical Staff, Thin Films Engineer</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Bratislava, Slovakia</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -13780,40 +13772,40 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>https://cisco.wd5.myworkdayjobs.com/job/Bratislava-Slovakia/Senior-Software-Engineer---Webex-Web-Client_2028673</t>
+          <t>https://intel.wd1.myworkdayjobs.com/job/US-Oregon-Hillsboro/Senior-Member-of-Technical-Staff--Thin-Films-Engineer_JR0284988</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:01.482006+00:00</t>
+          <t>2026-10-21T08:17:54.098511+00:00</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Cisco (Workday)</t>
+          <t>Intel (Workday)</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>WD-CISCO</t>
+          <t>WD-INTEL</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Staff Chemical Mechanical Planarization (CMP) Engineer</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Stockholm, Sweden</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -13835,40 +13827,40 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>https://cisco.wd5.myworkdayjobs.com/job/Stockholm-Sweden/Software-Engineer_2020685</t>
+          <t>https://intel.wd1.myworkdayjobs.com/job/US-Oregon-Hillsboro/Staff-Chemical-Mechanical-Planarization--CMP--Engineer_JR0285228</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:01.482006+00:00</t>
+          <t>2026-10-21T08:17:54.098511+00:00</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Intel (Workday)</t>
+          <t>Adobe (Workday)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>WD-INTEL</t>
+          <t>WD-ADOBE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Yield Product Development Engineer</t>
+          <t>Director of Engineering, Real Time Experience (RTX)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>3 Locations</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -13890,40 +13882,40 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>https://intel.wd1.myworkdayjobs.com/job/US-Oregon-Hillsboro/Yield-Product-Development-Engineer_JR0288027</t>
+          <t>https://adobe.wd5.myworkdayjobs.com/job/San-Jose/Director-of-Engineering--Real-Time-Experience--RTX-_R172776</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:03.082982+00:00</t>
+          <t>2026-10-21T08:17:55.845293+00:00</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Intel (Workday)</t>
+          <t>Adobe (Workday)</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>WD-INTEL</t>
+          <t>WD-ADOBE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Defect Metrology Engineer</t>
+          <t>Sr. Manager Risk &amp; Controls</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ireland, Leixlip</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -13945,40 +13937,40 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>https://intel.wd1.myworkdayjobs.com/job/Ireland-Leixlip/Defect-Metrology-Engineer_JR0284843</t>
+          <t>https://adobe.wd5.myworkdayjobs.com/job/San-Jose/Sr-Manager-Risk---Controls_R172265</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:03.082982+00:00</t>
+          <t>2026-10-21T08:17:55.845293+00:00</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Adobe (Workday)</t>
+          <t>Bosch Group (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>WD-ADOBE</t>
+          <t>SR-BOSCHGROUP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Sr. Manager Risk &amp; Controls</t>
+          <t>[PS-SC] パワートレインECU キャリブレーションエンジニア</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Bosch Group</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>Bosch Corporation_Higashimatsuyama_PS, jp</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -14000,40 +13992,40 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>https://adobe.wd5.myworkdayjobs.com/job/San-Jose/Sr-Manager-Risk---Controls_R172265</t>
+          <t>https://jobs.smartrecruiters.com/BoschGroup/744000156727777</t>
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:04.677693+00:00</t>
+          <t>2026-10-21T08:18:03.722219+00:00</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Adobe (Workday)</t>
+          <t>Bosch Group (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>WD-ADOBE</t>
+          <t>SR-BOSCHGROUP</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Director and Associate General Counsel, Corporate Legal</t>
+          <t>[GS] HR Intern (C&amp;B)- HCM Location</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Bosch Group</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>San Jose</t>
+          <t>Thành phố Hồ Chí Minh, vn</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -14055,40 +14047,40 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>https://adobe.wd5.myworkdayjobs.com/job/San-Jose/Director-and-Associate-General-Counsel--Corporate-Legal_R171220</t>
+          <t>https://jobs.smartrecruiters.com/BoschGroup/744000156728310</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:04.677693+00:00</t>
+          <t>2026-10-21T08:18:03.722219+00:00</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Bosch Group (SmartRecruiters)</t>
+          <t>ServiceNow (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SR-BOSCHGROUP</t>
+          <t>SR-SERVICENOW</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Channel Partner Manager – Linear Technologies (West Region)</t>
+          <t>Staff Inbound Product Manager</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Bosch Group</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pleasanton, us</t>
+          <t>Hyderabad, in</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14110,40 +14102,44 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/BoschGroup/744000155999850</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr"/>
+          <t>https://jobs.smartrecruiters.com/servicenow/744000156718589</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:10.466811+00:00</t>
+          <t>2026-10-21T08:18:04.642323+00:00</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Bosch Group (SmartRecruiters)</t>
+          <t>ServiceNow (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SR-BOSCHGROUP</t>
+          <t>SR-SERVICENOW</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Software Engineer - AI (f/m/div.)</t>
+          <t>Staff Software Engineer - Moveworks</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Bosch Group</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Lisboa, pt</t>
+          <t>Bangalore, in</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14165,40 +14161,44 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/BoschGroup/744000155993379</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr"/>
+          <t>https://jobs.smartrecruiters.com/servicenow/744000156713569</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Engineering, Infrastructure and Operations</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:10.466811+00:00</t>
+          <t>2026-10-21T08:18:04.642323+00:00</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ServiceNow (SmartRecruiters)</t>
+          <t>Accor (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SR-SERVICENOW</t>
+          <t>SR-ACCOR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Advisory Solution Consultant - Core Business Solutions</t>
+          <t>Pastry Chef</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Mumbai, in</t>
+          <t>Krong Siem Reap, kh</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -14220,44 +14220,40 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/servicenow/744000155944309</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>https://jobs.smartrecruiters.com/accor/744000156732539</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:10.960438+00:00</t>
+          <t>2026-10-21T08:18:05.142838+00:00</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ServiceNow (SmartRecruiters)</t>
+          <t>Accor (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SR-SERVICENOW</t>
+          <t>SR-ACCOR</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Principal Solution Consultant, CBS, Korea</t>
+          <t>Security Manager</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Seoul, kr</t>
+          <t>Krong Siem Reap, kh</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -14279,44 +14275,40 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/servicenow/744000155937210</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+          <t>https://jobs.smartrecruiters.com/accor/744000156731714</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:10.960438+00:00</t>
+          <t>2026-10-21T08:18:05.142838+00:00</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Accor (SmartRecruiters)</t>
+          <t>Avery Dennison (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SR-ACCOR</t>
+          <t>SR-AVERYDENNISON</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CHEF DE RECEPTION H/F</t>
+          <t>Quality Control Operative</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Clichy, fr</t>
+          <t>Harrogate, gb</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -14338,40 +14330,44 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/accor/744000155995170</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr"/>
+          <t>https://jobs.smartrecruiters.com/AveryDennison/744000156725605</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:11.507208+00:00</t>
+          <t>2026-10-21T08:18:05.647277+00:00</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Accor (SmartRecruiters)</t>
+          <t>Avery Dennison (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SR-ACCOR</t>
+          <t>SR-AVERYDENNISON</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Directeur de centrale de réservations en hôtellerie professionnelle (H/F)</t>
+          <t>Prozess-Chemiker (w/m/d)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Paris, fr</t>
+          <t>Kreuzlingen, ch</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -14393,40 +14389,44 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/accor/744000155992262</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr"/>
+          <t>https://jobs.smartrecruiters.com/AveryDennison/744000156720555</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:11.507208+00:00</t>
+          <t>2026-10-21T08:18:05.647277+00:00</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Avery Dennison (SmartRecruiters)</t>
+          <t>Swiggy (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SR-AVERYDENNISON</t>
+          <t>SR-SWIGGY</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Sales Manager II</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Swiggy</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mentor, us</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -14448,44 +14448,40 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AveryDennison/744000155993582</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>Engineering Services</t>
-        </is>
-      </c>
+          <t>https://jobs.smartrecruiters.com/swiggy/6000000001509488</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:12.028866+00:00</t>
+          <t>2026-10-21T08:18:07.047270+00:00</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Avery Dennison (SmartRecruiters)</t>
+          <t>Swiggy (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SR-AVERYDENNISON</t>
+          <t>SR-SWIGGY</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Operatore esperto addetto al taglio</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Swiggy</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cadorago, it</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -14507,44 +14503,40 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/AveryDennison/744000155994609</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
+          <t>https://jobs.smartrecruiters.com/swiggy/6000000001509159</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:12.029868+00:00</t>
+          <t>2026-10-21T08:18:07.047270+00:00</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Swiggy (SmartRecruiters)</t>
+          <t>Freshworks (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SR-SWIGGY</t>
+          <t>SR-FRESHWORKS</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Sales Manager I</t>
+          <t>Account Executive - Mid-Market</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Swiggy</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Kota, in</t>
+          <t>San Mateo, us</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -14566,40 +14558,40 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/swiggy/6000000001495795</t>
+          <t>https://jobs.smartrecruiters.com/freshworks/744000156661809</t>
         </is>
       </c>
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:13.369326+00:00</t>
+          <t>2026-10-21T08:18:07.517658+00:00</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Swiggy (SmartRecruiters)</t>
+          <t>Freshworks (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SR-SWIGGY</t>
+          <t>SR-FRESHWORKS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Sales Manager I</t>
+          <t>Account Executive - Mid-Market</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Swiggy</t>
+          <t>Freshworks</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Kurukshetra, in</t>
+          <t>Boston, us</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -14621,40 +14613,40 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/swiggy/6000000001495757</t>
+          <t>https://jobs.smartrecruiters.com/freshworks/744000156661749</t>
         </is>
       </c>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:13.369326+00:00</t>
+          <t>2026-10-21T08:18:07.517658+00:00</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Freshworks (SmartRecruiters)</t>
+          <t>Unacademy (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SR-FRESHWORKS</t>
+          <t>SR-UNACADEMY</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Senior Manager, Revenue Accounting</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>San Mateo, us</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -14676,35 +14668,35 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/freshworks/744000155865859</t>
+          <t>https://jobs.smartrecruiters.com/unacademy/743999710953763</t>
         </is>
       </c>
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:13.861975+00:00</t>
+          <t>2026-10-21T08:18:08.020940+00:00</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Freshworks (SmartRecruiters)</t>
+          <t>Unacademy (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SR-FRESHWORKS</t>
+          <t>SR-UNACADEMY</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Staff Engineer - Machine Learning</t>
+          <t>Business Development Executive</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Freshworks</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14731,40 +14723,40 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/freshworks/744000155675855</t>
+          <t>https://jobs.smartrecruiters.com/unacademy/743999710952745</t>
         </is>
       </c>
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:13.861975+00:00</t>
+          <t>2026-10-21T08:18:08.020940+00:00</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Unacademy (SmartRecruiters)</t>
+          <t>Cars24 (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SR-UNACADEMY</t>
+          <t>SR-CARS24</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Retail Associate</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Cars24</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Mumbai, in</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -14786,40 +14778,40 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/unacademy/743999710953763</t>
+          <t>https://jobs.smartrecruiters.com/cars24/743999664899164</t>
         </is>
       </c>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:14.367615+00:00</t>
+          <t>2026-10-21T08:18:08.525967+00:00</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Unacademy (SmartRecruiters)</t>
+          <t>Colliers (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SR-UNACADEMY</t>
+          <t>SR-COLLIERS</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Business Development Executive</t>
+          <t>Assistant Project Manager</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Colliers</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Canberra, au</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -14841,40 +14833,44 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/unacademy/743999710952745</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr"/>
+          <t>https://jobs.smartrecruiters.com/Colliers/744000156458669</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:14.367615+00:00</t>
+          <t>2026-10-21T08:18:09.055812+00:00</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Cars24 (SmartRecruiters)</t>
+          <t>Colliers (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SR-CARS24</t>
+          <t>SR-COLLIERS</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Retail Associate</t>
+          <t>Senior Commercial Property Manager</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Cars24</t>
+          <t>Colliers</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mumbai, in</t>
+          <t>Adelaide, au</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -14896,40 +14892,44 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/cars24/743999664899164</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr"/>
+          <t>https://jobs.smartrecruiters.com/Colliers/744000156226911</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Real Estate Management Services</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:14.874343+00:00</t>
+          <t>2026-10-21T08:18:09.055812+00:00</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Colliers (SmartRecruiters)</t>
+          <t>SGS (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SR-COLLIERS</t>
+          <t>SR-SGS</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Manager, Office Capital Markets &amp; Investment Services</t>
+          <t>HSE Officer – Oil &amp; Gas Shutdown Project</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Colliers</t>
+          <t>SGS</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Liverpool, au</t>
+          <t>Sohar, om</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -14951,44 +14951,44 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Colliers/744000155866899</t>
+          <t>https://jobs.smartrecruiters.com/SGS/744000156728578</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Capital Markets &amp; Investment Services</t>
+          <t>Inspection and Field Testing</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:15.421098+00:00</t>
+          <t>2026-10-21T08:18:09.558652+00:00</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Colliers (SmartRecruiters)</t>
+          <t>SGS (SmartRecruiters)</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SR-COLLIERS</t>
+          <t>SR-SGS</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Industrial Sales &amp; Leasing Executive</t>
+          <t>AP Accountant</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Colliers</t>
+          <t>SGS</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Chadstone, au</t>
+          <t>Hyderabad, in</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -15010,135 +15010,17 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Colliers/744000155405939</t>
+          <t>https://jobs.smartrecruiters.com/SGS/744000156722469</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Management, General Administration and Support Functions</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>2026-10-16T14:15:15.421098+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>SGS (SmartRecruiters)</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>SR-SGS</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Laboratory Technician</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>SGS</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Middlesbrough, gb</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/SGS/744000155997519</t>
-        </is>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>Laboratory &amp; Testing</t>
-        </is>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>2026-10-16T14:15:15.894401+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>SGS (SmartRecruiters)</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>SR-SGS</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Werken &amp; Leren Medewerker Buitendienst Regio Eindhoven - Den Bosch</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>SGS</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Heeswijk Dinther, nl</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>full_time</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/SGS/744000155985979</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>Inspection and Field Testing</t>
-        </is>
-      </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>2026-10-16T14:15:15.894401+00:00</t>
+          <t>2026-10-21T08:18:09.559651+00:00</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15077,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
